--- a/output/pdf_financials_xlsx/EDDY.xlsx
+++ b/output/pdf_financials_xlsx/EDDY.xlsx
@@ -5617,46 +5617,46 @@
         <v>0.242242</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.263704</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.398906</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.398745</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.407287</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.437036</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.581902</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.702989</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.702989</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.702989</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.634119</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>3.138937</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>1.954412</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>2.189289</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>2.189289</v>
       </c>
     </row>
     <row r="93">
@@ -7042,7 +7042,7 @@
         <v>0</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-0.127244</v>
       </c>
       <c r="F118" s="3" t="n">
         <v>0.199379</v>
@@ -7063,13 +7063,13 @@
         <v>-0.240731</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-0.142501</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>-0.3</v>
+        <v>-0.349628</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0.039118</v>
+        <v>-0.452577</v>
       </c>
       <c r="O118" s="3" t="n">
         <v>0.162364</v>
@@ -9424,7 +9424,11 @@
           <t>Reserve 7</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -10760,7 +10764,11 @@
           <t>Reserve 6</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -12020,7 +12028,11 @@
           <t>Reserve 8</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -12772,7 +12784,11 @@
           <t>Reserve 5</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -13752,7 +13768,11 @@
           <t>Reserve 4</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -14398,7 +14418,11 @@
           <t>Reserves 4</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -14980,7 +15004,11 @@
           <t>Reserves 4</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -15452,7 +15480,11 @@
           <t>Reserve</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E79" s="5" t="n">
         <v>0.057</v>
       </c>
@@ -20382,7 +20414,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -21524,7 +21560,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
@@ -23132,7 +23172,11 @@
           <t>Accrued exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -27020,7 +27064,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/EDDY.xlsx
+++ b/output/pdf_financials_xlsx/EDDY.xlsx
@@ -1020,25 +1020,25 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.00156</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.008489999999999999</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.002998</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003077</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001833</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00016</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-2e-06</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0</v>
@@ -1050,19 +1050,19 @@
         <v>0</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001559</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.038062</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.070969</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.039377</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>-0.019658</v>
       </c>
     </row>
     <row r="13">
@@ -1941,25 +1941,25 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.318163</v>
+        <v>-0.319723</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.434345</v>
+        <v>-0.442835</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.413042</v>
+        <v>-0.41604</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.505429</v>
+        <v>-0.502352</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.222029</v>
+        <v>-0.220196</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.264637</v>
+        <v>-0.264477</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.569015</v>
+        <v>-0.569013</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-1.027495</v>
@@ -1971,19 +1971,19 @@
         <v>-0.084734</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.528066</v>
+        <v>-1.526507</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-1.45098</v>
+        <v>-1.412918</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.9133019999999999</v>
+        <v>-0.842333</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-1.392389</v>
+        <v>-1.353012</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.487836</v>
+        <v>-0.468178</v>
       </c>
     </row>
     <row r="28">
@@ -2055,25 +2055,25 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.318163</v>
+        <v>-0.319723</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.434345</v>
+        <v>-0.442835</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.413042</v>
+        <v>-0.41604</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.505429</v>
+        <v>-0.502352</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.222029</v>
+        <v>-0.220196</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.264637</v>
+        <v>-0.264477</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.569015</v>
+        <v>-0.569013</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-1.027495</v>
@@ -2085,19 +2085,19 @@
         <v>-0.084734</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.528066</v>
+        <v>-1.526507</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-1.45098</v>
+        <v>-1.412918</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.9133019999999999</v>
+        <v>-0.842333</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-1.392389</v>
+        <v>-1.353012</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.487836</v>
+        <v>-0.468178</v>
       </c>
     </row>
     <row r="30">
@@ -2345,37 +2345,37 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.027663</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.13774</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.073528</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.611392</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.344722</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.125272</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.07431400000000001</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.296962</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.281273</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.978156</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.718574</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>3.715808</v>
@@ -2455,37 +2455,37 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.027663</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.13774</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.073528</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.611392</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.004</v>
+        <v>0.348722</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.125272</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.07431400000000001</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.296962</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.281273</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.978156</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.718574</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>3.715808</v>
@@ -3115,37 +3115,37 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.190366</v>
+        <v>0.162703</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.876678</v>
+        <v>0.738938</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.569354</v>
+        <v>0.495826</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.61449</v>
+        <v>0.003098</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.344722</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.134402</v>
+        <v>0.009129999999999999</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.087085</v>
+        <v>0.012771</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.418495</v>
+        <v>0.121533</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.701088</v>
+        <v>0.419815</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.001373</v>
+        <v>0.023217</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.7235740000000001</v>
+        <v>0.005</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>0.02886</v>
@@ -12316,7 +12316,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E45" s="5" t="n">
@@ -15578,7 +15578,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E80" s="5" t="n">
@@ -29768,7 +29768,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -42710,7 +42710,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
@@ -46334,7 +46334,7 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
